--- a/data_lake/datos_diarios_preliminares/dt=2026-07-31/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-31/temperaturamed.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8ABFE9E-C7F3-448E-AE03-A29A10A40835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95F5F0E-2458-441F-BA82-607E6154E767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$AM$1:$AM$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="116" width="32.42578125" style="50" customWidth="1"/>
-    <col min="117" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="118" width="32.42578125" style="50" customWidth="1"/>
+    <col min="119" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6725,15 +6724,17 @@
       <c r="AM5" s="56">
         <v>29.7</v>
       </c>
-      <c r="AN5" s="56"/>
+      <c r="AN5" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>28.827586206896552</v>
+        <v>28.853333333333335</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6741,7 +6742,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>0.67437131792528149</v>
+        <v>0.70011844436206516</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6862,15 +6863,17 @@
       <c r="AM6" s="56">
         <v>28.8</v>
       </c>
-      <c r="AN6" s="56"/>
+      <c r="AN6" s="56">
+        <v>29.3</v>
+      </c>
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>28.806896551724137</v>
+        <v>28.823333333333331</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6878,7 +6881,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>0.41166266277531705</v>
+        <v>0.42809944438451097</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6999,15 +7002,17 @@
       <c r="AM7" s="56">
         <v>32</v>
       </c>
-      <c r="AN7" s="56"/>
+      <c r="AN7" s="56">
+        <v>32.9</v>
+      </c>
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.413793103448278</v>
+        <v>31.463333333333331</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7015,7 +7020,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.2136126118968171</v>
+        <v>2.2631528417818707</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7136,15 +7141,17 @@
       <c r="AM8" s="56">
         <v>30.9</v>
       </c>
-      <c r="AN8" s="56"/>
+      <c r="AN8" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.727586206896554</v>
+        <v>29.783333333333335</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7152,7 +7159,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.1490468907251525</v>
+        <v>1.2047940171619338</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7273,15 +7280,17 @@
       <c r="AM9" s="56">
         <v>30.9</v>
       </c>
-      <c r="AN9" s="56"/>
+      <c r="AN9" s="56">
+        <v>31.5</v>
+      </c>
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.424137931034487</v>
+        <v>29.493333333333336</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7289,7 +7298,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>-0.3633310515957433</v>
+        <v>-0.29413564929689429</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7410,15 +7419,17 @@
       <c r="AM10" s="56">
         <v>33</v>
       </c>
-      <c r="AN10" s="56"/>
+      <c r="AN10" s="56">
+        <v>32.5</v>
+      </c>
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>31.631034482758619</v>
+        <v>31.66</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7426,7 +7437,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>1.5516124483535592</v>
+        <v>1.5805779655949408</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7547,15 +7558,17 @@
       <c r="AM11" s="56">
         <v>34.4</v>
       </c>
-      <c r="AN11" s="56"/>
+      <c r="AN11" s="56">
+        <v>34.4</v>
+      </c>
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.627586206896552</v>
+        <v>32.686666666666667</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7563,7 +7576,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>2.6236721296687016</v>
+        <v>2.6827525894388167</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7684,15 +7697,17 @@
       <c r="AM12" s="56">
         <v>31</v>
       </c>
-      <c r="AN12" s="56"/>
+      <c r="AN12" s="56">
+        <v>31.3</v>
+      </c>
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>30.020689655172408</v>
+        <v>30.063333333333325</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7700,7 +7715,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.7550232658568277</v>
+        <v>1.7976669440177453</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7821,15 +7836,17 @@
       <c r="AM13" s="56">
         <v>31.4</v>
       </c>
-      <c r="AN13" s="56"/>
+      <c r="AN13" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>29.993103448275857</v>
+        <v>30.023333333333326</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7837,7 +7854,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.6637087504634955</v>
+        <v>1.6939386355209649</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7958,15 +7975,17 @@
       <c r="AM14" s="56">
         <v>25</v>
       </c>
-      <c r="AN14" s="56"/>
+      <c r="AN14" s="56">
+        <v>25.9</v>
+      </c>
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.665517241379309</v>
+        <v>23.74</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7974,7 +7993,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.9439772174844592</v>
+        <v>2.0184599761051487</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8095,15 +8114,17 @@
       <c r="AM15" s="56">
         <v>31.5</v>
       </c>
-      <c r="AN15" s="56"/>
+      <c r="AN15" s="56">
+        <v>30.9</v>
+      </c>
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.337931034482757</v>
+        <v>29.389999999999997</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8111,7 +8132,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>1.102425658138678</v>
+        <v>1.1544946236559177</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8232,15 +8253,17 @@
       <c r="AM16" s="56">
         <v>29.6</v>
       </c>
-      <c r="AN16" s="56"/>
+      <c r="AN16" s="56">
+        <v>30.2</v>
+      </c>
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.413793103448281</v>
+        <v>28.47333333333334</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8248,7 +8271,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.77614025504530204</v>
+        <v>0.83568048493036073</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8369,15 +8392,17 @@
       <c r="AM17" s="56">
         <v>26.3</v>
       </c>
-      <c r="AN17" s="56"/>
+      <c r="AN17" s="56">
+        <v>26.7</v>
+      </c>
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>24.689655172413797</v>
+        <v>24.756666666666671</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8385,7 +8410,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.70603150325759856</v>
+        <v>0.77304299751047267</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8506,15 +8531,17 @@
       <c r="AM18" s="56">
         <v>19.7</v>
       </c>
-      <c r="AN18" s="56"/>
+      <c r="AN18" s="56">
+        <v>19.8</v>
+      </c>
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.80344827586207</v>
+        <v>18.836666666666666</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8522,7 +8549,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.3850970213817888</v>
+        <v>1.4183154121863843</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8643,15 +8670,17 @@
       <c r="AM19" s="56">
         <v>25.3</v>
       </c>
-      <c r="AN19" s="56"/>
+      <c r="AN19" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.265517241379307</v>
+        <v>24.326666666666664</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8659,7 +8688,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.1319822951427554</v>
+        <v>2.1931317204301131</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8780,15 +8809,17 @@
       <c r="AM20" s="56">
         <v>25</v>
       </c>
-      <c r="AN20" s="56"/>
+      <c r="AN20" s="56">
+        <v>26</v>
+      </c>
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>24.320689655172409</v>
+        <v>24.376666666666662</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8796,7 +8827,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.7130242292005384</v>
+        <v>1.7690012406947915</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8917,15 +8948,17 @@
       <c r="AM21" s="56">
         <v>27</v>
       </c>
-      <c r="AN21" s="56"/>
+      <c r="AN21" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>27.151724137931033</v>
+        <v>27.24</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8933,7 +8966,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>2.461642246173902</v>
+        <v>2.549918108242867</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9054,15 +9087,17 @@
       <c r="AM22" s="56">
         <v>16.2</v>
       </c>
-      <c r="AN22" s="56"/>
+      <c r="AN22" s="56">
+        <v>15.3</v>
+      </c>
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.506896551724138</v>
+        <v>15.5</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9070,7 +9105,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.726563631955738</v>
+        <v>1.7196670802316003</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9191,15 +9226,17 @@
       <c r="AM23" s="56">
         <v>26.3</v>
       </c>
-      <c r="AN23" s="56"/>
+      <c r="AN23" s="56">
+        <v>27.5</v>
+      </c>
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.082758620689649</v>
+        <v>26.129999999999995</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9328,15 +9365,17 @@
       <c r="AM24" s="56">
         <v>30.5</v>
       </c>
-      <c r="AN24" s="56"/>
+      <c r="AN24" s="56">
+        <v>30.7</v>
+      </c>
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.479310344827589</v>
+        <v>29.520000000000003</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9344,7 +9383,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.1169518600914685</v>
+        <v>1.157641515263883</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9465,15 +9504,17 @@
       <c r="AM25" s="56">
         <v>21.7</v>
       </c>
-      <c r="AN25" s="56"/>
+      <c r="AN25" s="56">
+        <v>23.4</v>
+      </c>
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>21.844827586206897</v>
+        <v>21.896666666666665</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9481,7 +9522,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.9114031300046967</v>
+        <v>1.9632422104644647</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9602,15 +9643,17 @@
       <c r="AM26" s="56">
         <v>9.4</v>
       </c>
-      <c r="AN26" s="56"/>
+      <c r="AN26" s="56">
+        <v>11.8</v>
+      </c>
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.444827586206895</v>
+        <v>11.456666666666665</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9618,7 +9661,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.0745126860533052</v>
+        <v>1.0863517665130757</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9739,15 +9782,17 @@
       <c r="AM27" s="56">
         <v>30.1</v>
       </c>
-      <c r="AN27" s="56"/>
+      <c r="AN27" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>28.148275862068971</v>
+        <v>28.160000000000007</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9755,7 +9800,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.1595698924731224</v>
+        <v>1.1712940304041588</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9876,15 +9921,17 @@
       <c r="AM28" s="56">
         <v>27.2</v>
       </c>
-      <c r="AN28" s="56"/>
+      <c r="AN28" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>26.617241379310347</v>
+        <v>26.660000000000004</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9892,7 +9939,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>0.86582282783340503</v>
+        <v>0.90858144852306211</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -10013,15 +10060,17 @@
       <c r="AM29" s="56">
         <v>29.1</v>
       </c>
-      <c r="AN29" s="56"/>
+      <c r="AN29" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>27.80344827586207</v>
+        <v>27.860000000000003</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10029,7 +10078,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.84940606160483156</v>
+        <v>0.90595778574276409</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10150,15 +10199,17 @@
       <c r="AM30" s="56">
         <v>23.3</v>
       </c>
-      <c r="AN30" s="56"/>
+      <c r="AN30" s="56">
+        <v>26</v>
+      </c>
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>25.286206896551722</v>
+        <v>25.31</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10166,7 +10217,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.7682054134223506</v>
+        <v>0.79199851687062761</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -10287,15 +10338,17 @@
       <c r="AM31" s="98">
         <v>28</v>
       </c>
-      <c r="AN31" s="98"/>
+      <c r="AN31" s="98">
+        <v>27.1</v>
+      </c>
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>26.844827586206897</v>
+        <v>26.853333333333335</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10303,7 +10356,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4758789601614986</v>
+        <v>1.484384707287937</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10424,15 +10477,17 @@
       <c r="AM32" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="AN32" s="56"/>
+      <c r="AN32" s="56">
+        <v>19.666666666666671</v>
+      </c>
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.442528735632184</v>
+        <v>20.416666666666668</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10440,7 +10495,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.7856726835233445</v>
+        <v>2.7598106145578285</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10561,15 +10616,17 @@
       <c r="AM33" s="56">
         <v>29</v>
       </c>
-      <c r="AN33" s="56"/>
+      <c r="AN33" s="56">
+        <v>28.95</v>
+      </c>
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.970689655172418</v>
+        <v>28.003333333333337</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10577,7 +10634,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.1432175739598662</v>
+        <v>1.1758612521207858</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10698,15 +10755,17 @@
       <c r="AM34" s="56">
         <v>22.333333333333329</v>
       </c>
-      <c r="AN34" s="56"/>
+      <c r="AN34" s="56">
+        <v>22</v>
+      </c>
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.328735632183911</v>
+        <v>21.351111111111113</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10714,7 +10773,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.541538040503589</v>
+        <v>1.5639135194307912</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10835,15 +10894,17 @@
       <c r="AM35" s="56">
         <v>25.1</v>
       </c>
-      <c r="AN35" s="56"/>
+      <c r="AN35" s="56">
+        <v>24.65</v>
+      </c>
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.553448275862067</v>
+        <v>24.556666666666665</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10851,7 +10912,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.51520037614466574</v>
+        <v>0.5184187669492637</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10972,15 +11033,17 @@
       <c r="AM36" s="56">
         <v>19.7</v>
       </c>
-      <c r="AN36" s="56"/>
+      <c r="AN36" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.967241379310348</v>
+        <v>19.988333333333337</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10988,7 +11051,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>0.96843031609195762</v>
+        <v>0.98952227011494642</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11109,15 +11172,17 @@
       <c r="AM37" s="56">
         <v>27.55</v>
       </c>
-      <c r="AN37" s="56"/>
+      <c r="AN37" s="56">
+        <v>27.95</v>
+      </c>
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>27.375862068965517</v>
+        <v>27.395</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11125,7 +11190,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.4896321950281362</v>
+        <v>1.5087701260626183</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11242,15 +11307,17 @@
       <c r="AM38" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AN38" s="56"/>
+      <c r="AN38" s="56">
+        <v>16.899999999999999</v>
+      </c>
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.916666666666666</v>
+        <v>15.951785714285714</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11258,7 +11325,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.89873765971598552</v>
+        <v>0.93385670733503368</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11377,15 +11444,17 @@
       <c r="AM39" s="56">
         <v>23</v>
       </c>
-      <c r="AN39" s="56"/>
+      <c r="AN39" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.259523809523809</v>
+        <v>22.360919540229887</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11502,15 +11571,17 @@
       <c r="AM40" s="56">
         <v>25.93333333333333</v>
       </c>
-      <c r="AN40" s="56"/>
+      <c r="AN40" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.223913043478255</v>
+        <v>25.292361111111106</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11518,7 +11589,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.3721222950512839</v>
+        <v>2.4405703626841344</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11637,15 +11708,17 @@
       <c r="AM41" s="56">
         <v>20.733333333333331</v>
       </c>
-      <c r="AN41" s="56"/>
+      <c r="AN41" s="56">
+        <v>19.333333333333329</v>
+      </c>
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>20.082142857142852</v>
+        <v>20.056321839080457</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11653,7 +11726,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>1.5900336658151133</v>
+        <v>1.5642126477527185</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11774,15 +11847,17 @@
       <c r="AM42" s="56">
         <v>28.9</v>
       </c>
-      <c r="AN42" s="56"/>
+      <c r="AN42" s="56">
+        <v>29.15</v>
+      </c>
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.969827586206893</v>
+        <v>28.009166666666662</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11790,7 +11865,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.21714206914862189</v>
+        <v>0.25648114960839052</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11907,15 +11982,17 @@
       <c r="AM43" s="56">
         <v>30.35</v>
       </c>
-      <c r="AN43" s="56"/>
+      <c r="AN43" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.300000000000004</v>
+        <v>29.346428571428579</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12044,15 +12121,17 @@
       <c r="AM44" s="56">
         <v>28.75</v>
       </c>
-      <c r="AN44" s="56"/>
+      <c r="AN44" s="56">
+        <v>29.55</v>
+      </c>
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.520689655172411</v>
+        <v>28.554999999999996</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12060,7 +12139,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.1783462108895897</v>
+        <v>1.2126565557171745</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12181,15 +12260,17 @@
       <c r="AM45" s="56">
         <v>29.4</v>
       </c>
-      <c r="AN45" s="56"/>
+      <c r="AN45" s="56">
+        <v>30.15</v>
+      </c>
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>29.17413793103449</v>
+        <v>29.206666666666671</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12197,7 +12278,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>1.4060304561030605</v>
+        <v>1.4385591917352407</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12318,15 +12399,17 @@
       <c r="AM46" s="56">
         <v>29.7</v>
       </c>
-      <c r="AN46" s="56"/>
+      <c r="AN46" s="56">
+        <v>29.9</v>
+      </c>
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.907758620689656</v>
+        <v>28.940833333333334</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12334,7 +12417,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.0015609887921748</v>
+        <v>1.0346357014358532</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12455,15 +12538,17 @@
       <c r="AM47" s="56">
         <v>31.333333333333329</v>
       </c>
-      <c r="AN47" s="56"/>
+      <c r="AN47" s="56">
+        <v>31.733333333333331</v>
+      </c>
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ47" s="71">
         <f t="shared" si="1"/>
-        <v>29.94367816091955</v>
+        <v>30.003333333333341</v>
       </c>
       <c r="AR47" s="71">
         <f>IFERROR(VLOOKUP(A47,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12471,7 +12556,7 @@
       </c>
       <c r="AS47" s="71">
         <f t="shared" si="2"/>
-        <v>1.9748023016021605</v>
+        <v>2.0344574740159516</v>
       </c>
     </row>
     <row r="48" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12750,15 +12835,17 @@
       <c r="AM50" s="56">
         <v>29.45</v>
       </c>
-      <c r="AN50" s="56"/>
+      <c r="AN50" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>29.213793103448275</v>
+        <v>29.259999999999998</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12766,7 +12853,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.9251027574164539</v>
+        <v>1.9713096539681771</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13073,15 +13160,17 @@
       <c r="AM53" s="56">
         <v>29.35</v>
       </c>
-      <c r="AN53" s="56"/>
+      <c r="AN53" s="56">
+        <v>30.35</v>
+      </c>
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>28.841379310344827</v>
+        <v>28.891666666666666</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13089,7 +13178,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>1.4821330137542787</v>
+        <v>1.5324203700761174</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13210,15 +13299,17 @@
       <c r="AM54" s="56">
         <v>30.75</v>
       </c>
-      <c r="AN54" s="56"/>
+      <c r="AN54" s="56">
+        <v>31.9</v>
+      </c>
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>30.003448275862077</v>
+        <v>30.066666666666674</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13226,7 +13317,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.5052222507956579</v>
+        <v>1.5684406416002545</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13333,15 +13424,17 @@
       <c r="AM55" s="56">
         <v>30.7</v>
       </c>
-      <c r="AN55" s="56"/>
+      <c r="AN55" s="56">
+        <v>31.5</v>
+      </c>
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ55" s="71">
         <f t="shared" si="1"/>
-        <v>30.193181818181827</v>
+        <v>30.250000000000011</v>
       </c>
       <c r="AR55" s="71">
         <f>IFERROR(VLOOKUP(A55,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13349,7 +13442,7 @@
       </c>
       <c r="AS55" s="71">
         <f t="shared" si="2"/>
-        <v>1.7622221479447866</v>
+        <v>1.81904032976297</v>
       </c>
     </row>
     <row r="56" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13470,15 +13563,17 @@
       <c r="AM56" s="56">
         <v>28.9</v>
       </c>
-      <c r="AN56" s="56"/>
+      <c r="AN56" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AO56" s="56"/>
       <c r="AP56" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ56" s="71">
         <f t="shared" si="1"/>
-        <v>29.275862068965516</v>
+        <v>29.32</v>
       </c>
       <c r="AR56" s="71" t="str">
         <f>IFERROR(VLOOKUP(A56,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13763,15 +13858,17 @@
       <c r="AM59" s="56">
         <v>29.55</v>
       </c>
-      <c r="AN59" s="56"/>
+      <c r="AN59" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.059821428571428</v>
+        <v>29.095689655172414</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13779,7 +13876,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.94560159948926881</v>
+        <v>0.98146982609025457</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14025,15 +14122,17 @@
       <c r="AM61" s="56">
         <v>27.85</v>
       </c>
-      <c r="AN61" s="56"/>
+      <c r="AN61" s="56">
+        <v>26.95</v>
+      </c>
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>26.789655172413799</v>
+        <v>26.795000000000009</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14041,7 +14140,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.0829834906878375</v>
+        <v>1.0883283182740477</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14162,15 +14261,17 @@
       <c r="AM62" s="56">
         <v>27.066666666666659</v>
       </c>
-      <c r="AN62" s="56"/>
+      <c r="AN62" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>26.080459770114945</v>
+        <v>26.062222222222221</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14178,7 +14279,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.5414558301510546</v>
+        <v>1.5232182822583304</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14439,15 +14540,17 @@
       <c r="AM65" s="56">
         <v>26.9</v>
       </c>
-      <c r="AN65" s="56"/>
+      <c r="AN65" s="56">
+        <v>24.05</v>
+      </c>
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>25.815000000000005</v>
+        <v>25.730952380952381</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14455,7 +14558,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.80979404168884628</v>
+        <v>0.72574642264122247</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14576,15 +14679,17 @@
       <c r="AM66" s="56">
         <v>27</v>
       </c>
-      <c r="AN66" s="56"/>
+      <c r="AN66" s="56">
+        <v>23.55</v>
+      </c>
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>25.791379310344823</v>
+        <v>25.716666666666658</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14592,7 +14697,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.88226448006583169</v>
+        <v>0.80755183638766681</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14709,15 +14814,17 @@
       <c r="AM67" s="56">
         <v>24.3</v>
       </c>
-      <c r="AN67" s="56"/>
+      <c r="AN67" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>25.570370370370366</v>
+        <v>25.571428571428566</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14725,7 +14832,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.91916345853915615</v>
+        <v>0.92022165959735602</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14846,15 +14953,17 @@
       <c r="AM68" s="56">
         <v>23.9</v>
       </c>
-      <c r="AN68" s="56"/>
+      <c r="AN68" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.532758620689652</v>
+        <v>25.521666666666665</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14862,7 +14971,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>1.0076711179466322</v>
+        <v>0.99657916392364498</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14983,15 +15092,17 @@
       <c r="AM69" s="56">
         <v>24.15</v>
       </c>
-      <c r="AN69" s="56"/>
+      <c r="AN69" s="56">
+        <v>25.75</v>
+      </c>
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>24.968103448275869</v>
+        <v>24.994166666666672</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14999,7 +15110,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.6457057616438604</v>
+        <v>0.67176898003466334</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15106,15 +15217,17 @@
       <c r="AM70" s="56">
         <v>26.733333333333331</v>
       </c>
-      <c r="AN70" s="56"/>
+      <c r="AN70" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ70" s="71">
         <f t="shared" si="4"/>
-        <v>26.583333333333336</v>
+        <v>26.572463768115945</v>
       </c>
       <c r="AR70" s="71">
         <f>IFERROR(VLOOKUP(A70,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15122,7 +15235,7 @@
       </c>
       <c r="AS70" s="71">
         <f t="shared" si="5"/>
-        <v>1.0133746422901346</v>
+        <v>1.0025050770727439</v>
       </c>
     </row>
     <row r="71" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15243,15 +15356,17 @@
       <c r="AM71" s="56">
         <v>26.233333333333331</v>
       </c>
-      <c r="AN71" s="56"/>
+      <c r="AN71" s="56">
+        <v>25.56666666666667</v>
+      </c>
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>25.99080459770115</v>
+        <v>25.97666666666667</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15259,7 +15374,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.32836168404762134</v>
+        <v>0.31422375301314176</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15378,15 +15493,17 @@
       <c r="AM72" s="56">
         <v>25.3</v>
       </c>
-      <c r="AN72" s="56"/>
+      <c r="AN72" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>25.401190476190475</v>
+        <v>25.435632183908044</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15394,7 +15511,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.42798173323093636</v>
+        <v>0.46242344094850552</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15499,15 +15616,17 @@
       <c r="AM73" s="56">
         <v>24.05</v>
       </c>
-      <c r="AN73" s="56"/>
+      <c r="AN73" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ73" s="71">
         <f t="shared" si="4"/>
-        <v>25.776190476190475</v>
+        <v>25.765909090909087</v>
       </c>
       <c r="AR73" s="71" t="str">
         <f>IFERROR(VLOOKUP(A73,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15636,15 +15755,17 @@
       <c r="AM74" s="56">
         <v>21.3</v>
       </c>
-      <c r="AN74" s="56"/>
+      <c r="AN74" s="56">
+        <v>20.05</v>
+      </c>
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>20.933620689655172</v>
+        <v>20.904166666666661</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15652,7 +15773,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>0.9351219402950619</v>
+        <v>0.90566791730655183</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15773,15 +15894,17 @@
       <c r="AM75" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="AN75" s="56"/>
+      <c r="AN75" s="56">
+        <v>16.333333333333329</v>
+      </c>
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>15.874712643678157</v>
+        <v>15.889999999999995</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15789,7 +15912,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.69366895171136633</v>
+        <v>0.70895630803320486</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15910,15 +16033,17 @@
       <c r="AM76" s="56">
         <v>21.9</v>
       </c>
-      <c r="AN76" s="56"/>
+      <c r="AN76" s="56">
+        <v>20.5</v>
+      </c>
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>20.768103448275863</v>
+        <v>20.759166666666665</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15926,7 +16051,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>0.96813683674964324</v>
+        <v>0.95920005514044604</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16047,15 +16172,17 @@
       <c r="AM77" s="56">
         <v>23.866666666666671</v>
       </c>
-      <c r="AN77" s="56"/>
+      <c r="AN77" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>24.020689655172408</v>
+        <v>24.013333333333325</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16063,7 +16190,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.3374487991934885</v>
+        <v>1.3300924773544054</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16184,15 +16311,17 @@
       <c r="AM78" s="56">
         <v>32.5</v>
       </c>
-      <c r="AN78" s="56"/>
+      <c r="AN78" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>31.232758620689655</v>
+        <v>31.251666666666665</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16200,7 +16329,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>2.0488288101670058</v>
+        <v>2.0677368561440161</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16317,15 +16446,17 @@
       <c r="AM79" s="56">
         <v>32.133333333333333</v>
       </c>
-      <c r="AN79" s="56"/>
+      <c r="AN79" s="56">
+        <v>31.733333333333331</v>
+      </c>
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>31.32839506172839</v>
+        <v>31.342857142857138</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16333,7 +16464,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>1.8593421772776608</v>
+        <v>1.873804258406409</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16585,15 +16716,17 @@
       <c r="AM81" s="56">
         <v>24.8</v>
       </c>
-      <c r="AN81" s="56"/>
+      <c r="AN81" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ81" s="71">
         <f t="shared" si="4"/>
-        <v>24.2326923076923</v>
+        <v>24.281481481481475</v>
       </c>
       <c r="AR81" s="71">
         <f>IFERROR(VLOOKUP(A81,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16601,7 +16734,7 @@
       </c>
       <c r="AS81" s="71">
         <f t="shared" si="5"/>
-        <v>5.8062401600530222E-2</v>
+        <v>0.10685157538970458</v>
       </c>
     </row>
     <row r="82" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16722,15 +16855,17 @@
       <c r="AM82" s="56">
         <v>25.333333333333329</v>
       </c>
-      <c r="AN82" s="56"/>
+      <c r="AN82" s="56">
+        <v>26.866666666666671</v>
+      </c>
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>26.242528735632188</v>
+        <v>26.263333333333335</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16738,7 +16873,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>1.0688062782106087</v>
+        <v>1.089610875911756</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16999,15 +17134,17 @@
       <c r="AM85" s="56">
         <v>32.25</v>
       </c>
-      <c r="AN85" s="56"/>
+      <c r="AN85" s="56">
+        <v>32.65</v>
+      </c>
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>30.859999999999996</v>
+        <v>30.945238095238089</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17136,15 +17273,17 @@
       <c r="AM86" s="56">
         <v>30.25</v>
       </c>
-      <c r="AN86" s="56"/>
+      <c r="AN86" s="56">
+        <v>30.6</v>
+      </c>
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.781034482758617</v>
+        <v>29.80833333333333</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17152,7 +17291,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.1689513212038278</v>
+        <v>1.1962501717785408</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17273,15 +17412,17 @@
       <c r="AM87" s="56">
         <v>31.95</v>
       </c>
-      <c r="AN87" s="56"/>
+      <c r="AN87" s="56">
+        <v>32.849999999999987</v>
+      </c>
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>31.551724137931043</v>
+        <v>31.59500000000001</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17289,7 +17430,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.5455341654686521</v>
+        <v>2.5888100275376189</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17410,15 +17551,17 @@
       <c r="AM88" s="56">
         <v>31.85</v>
       </c>
-      <c r="AN88" s="56"/>
+      <c r="AN88" s="56">
+        <v>32.049999999999997</v>
+      </c>
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.236206896551728</v>
+        <v>30.29666666666667</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17426,7 +17569,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>1.5453322805763179</v>
+        <v>1.6057920506912602</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17533,15 +17676,17 @@
         <v>32.900000000000013</v>
       </c>
       <c r="AM89" s="56"/>
-      <c r="AN89" s="56"/>
+      <c r="AN89" s="56">
+        <v>35.849999999999987</v>
+      </c>
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>33.154545454545456</v>
+        <v>33.271739130434781</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17549,7 +17694,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.6720464128987551</v>
+        <v>3.7892400887880804</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17781,15 +17926,17 @@
       <c r="AM91" s="56">
         <v>29.4</v>
       </c>
-      <c r="AN91" s="56"/>
+      <c r="AN91" s="56">
+        <v>35.450000000000003</v>
+      </c>
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>32.125000000000007</v>
+        <v>32.283333333333339</v>
       </c>
       <c r="AR91" s="71" t="str">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17918,15 +18065,17 @@
       <c r="AM92" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AN92" s="56"/>
+      <c r="AN92" s="56">
+        <v>19.649999999999999</v>
+      </c>
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>17.435632183908048</v>
+        <v>17.509444444444448</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17934,7 +18083,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>1.2722880978865767</v>
+        <v>1.3461003584229765</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18055,15 +18204,17 @@
       <c r="AM93" s="56">
         <v>24.466666666666669</v>
       </c>
-      <c r="AN93" s="56"/>
+      <c r="AN93" s="56">
+        <v>25.333333333333329</v>
+      </c>
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.678160919540229</v>
+        <v>23.733333333333334</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18071,7 +18222,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.5686730536706079</v>
+        <v>1.6238454674637133</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18192,15 +18343,17 @@
       <c r="AM94" s="56">
         <v>18.600000000000001</v>
       </c>
-      <c r="AN94" s="56"/>
+      <c r="AN94" s="56">
+        <v>17.55</v>
+      </c>
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.304310344827591</v>
+        <v>17.312500000000004</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18208,7 +18361,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.2090831988930226</v>
+        <v>1.2172728540654347</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18329,15 +18482,17 @@
       <c r="AM95" s="56">
         <v>15.45</v>
       </c>
-      <c r="AN95" s="56"/>
+      <c r="AN95" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.693103448275863</v>
+        <v>14.696666666666667</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18345,7 +18500,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.0602953121240031</v>
+        <v>1.0638585305148069</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18624,15 +18779,17 @@
       <c r="AM98" s="56">
         <v>13.8</v>
       </c>
-      <c r="AN98" s="56"/>
+      <c r="AN98" s="56">
+        <v>14.2</v>
+      </c>
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.129310344827585</v>
+        <v>13.164999999999999</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18754,16 +18911,20 @@
       <c r="AL99" s="56">
         <v>14.6</v>
       </c>
-      <c r="AM99" s="56"/>
-      <c r="AN99" s="56"/>
+      <c r="AM99" s="56">
+        <v>15.46666666666667</v>
+      </c>
+      <c r="AN99" s="56">
+        <v>15.06666666666667</v>
+      </c>
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.482051282051286</v>
+        <v>14.538095238095242</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18878,15 +19039,17 @@
       <c r="AM100" s="56">
         <v>15.53333333333333</v>
       </c>
-      <c r="AN100" s="56"/>
+      <c r="AN100" s="56">
+        <v>15.06666666666667</v>
+      </c>
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.145454545454545</v>
+        <v>16.098550724637679</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18894,7 +19057,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>1.8360966393465539</v>
+        <v>1.7891928185296884</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19001,15 +19164,17 @@
       <c r="AM101" s="56">
         <v>13.85</v>
       </c>
-      <c r="AN101" s="56"/>
+      <c r="AN101" s="56">
+        <v>13.7</v>
+      </c>
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.375000000000002</v>
+        <v>13.389130434782611</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19017,7 +19182,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.0425963373887122</v>
+        <v>1.0567267721713218</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19132,15 +19297,17 @@
       <c r="AM102" s="56">
         <v>13.733333333333331</v>
       </c>
-      <c r="AN102" s="56"/>
+      <c r="AN102" s="56">
+        <v>12.66666666666667</v>
+      </c>
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ102" s="71">
         <f t="shared" si="4"/>
-        <v>13.058974358974362</v>
+        <v>13.044444444444448</v>
       </c>
       <c r="AR102" s="71">
         <f>IFERROR(VLOOKUP(A102,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19148,7 +19315,7 @@
       </c>
       <c r="AS102" s="71">
         <f t="shared" si="5"/>
-        <v>1.8119789895884715</v>
+        <v>1.797449075058557</v>
       </c>
     </row>
     <row r="103" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19421,15 +19588,17 @@
       <c r="AM105" s="56">
         <v>19.399999999999999</v>
       </c>
-      <c r="AN105" s="56"/>
+      <c r="AN105" s="56">
+        <v>20</v>
+      </c>
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.215384615384615</v>
+        <v>18.281481481481482</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19437,7 +19606,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.1708471069083437</v>
+        <v>1.2369439730052108</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19750,15 +19919,17 @@
       <c r="AM108" s="56">
         <v>14.7</v>
       </c>
-      <c r="AN108" s="56"/>
+      <c r="AN108" s="56">
+        <v>14.9</v>
+      </c>
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>14.222413793103449</v>
+        <v>14.245000000000001</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19766,7 +19937,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-6.619121628361313E-3</v>
+        <v>1.5967085268190573E-2</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19887,15 +20058,17 @@
       <c r="AM109" s="56">
         <v>15.6</v>
       </c>
-      <c r="AN109" s="56"/>
+      <c r="AN109" s="56">
+        <v>15.75</v>
+      </c>
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.606896551724137</v>
+        <v>14.645</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19903,7 +20076,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.89313346421634776</v>
+        <v>0.93123691249220997</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20024,15 +20197,17 @@
       <c r="AM110" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="AN110" s="56"/>
+      <c r="AN110" s="56">
+        <v>17.399999999999999</v>
+      </c>
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.535632183908039</v>
+        <v>17.531111111111105</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20040,7 +20215,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.60067014544114983</v>
+        <v>0.59614907264421646</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20161,15 +20336,17 @@
       <c r="AM111" s="56">
         <v>17</v>
       </c>
-      <c r="AN111" s="56"/>
+      <c r="AN111" s="56">
+        <v>15.733333333333331</v>
+      </c>
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.93218390804598</v>
+        <v>15.925555555555558</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20177,7 +20354,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.42982038447279081</v>
+        <v>0.42319203198236899</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20298,15 +20475,17 @@
       <c r="AM112" s="56">
         <v>17.133333333333329</v>
       </c>
-      <c r="AN112" s="56"/>
+      <c r="AN112" s="56">
+        <v>17.866666666666671</v>
+      </c>
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>17.822988505747123</v>
+        <v>17.824444444444442</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20314,7 +20493,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.4432922446450434</v>
+        <v>1.4447481833423623</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20431,15 +20610,17 @@
         <v>19.2</v>
       </c>
       <c r="AM113" s="56"/>
-      <c r="AN113" s="56"/>
+      <c r="AN113" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v>19.022222222222222</v>
+        <v>19.00714285714286</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20447,7 +20628,7 @@
       </c>
       <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v>0.89783475466569129</v>
+        <v>0.88275538958632893</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20671,15 +20852,17 @@
       <c r="AM115" s="56">
         <v>26.3</v>
       </c>
-      <c r="AN115" s="56"/>
+      <c r="AN115" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>26.335344827586205</v>
+        <v>26.340833333333329</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20687,7 +20870,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.49086484983318357</v>
+        <v>0.49635335558030746</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20804,15 +20987,17 @@
       <c r="AM116" s="56">
         <v>19.8</v>
       </c>
-      <c r="AN116" s="56"/>
+      <c r="AN116" s="56">
+        <v>19</v>
+      </c>
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.271604938271608</v>
+        <v>19.261904761904763</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20820,7 +21005,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.87509977193078825</v>
+        <v>0.86539959556394308</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20941,15 +21126,17 @@
       <c r="AM117" s="56">
         <v>27</v>
       </c>
-      <c r="AN117" s="56"/>
+      <c r="AN117" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>26.31954022988506</v>
+        <v>26.337777777777781</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20957,7 +21144,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.95070062415031131</v>
+        <v>0.9689381720430319</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21078,15 +21265,17 @@
       <c r="AM118" s="56">
         <v>29.466666666666669</v>
       </c>
-      <c r="AN118" s="56"/>
+      <c r="AN118" s="56">
+        <v>29.866666666666671</v>
+      </c>
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ118" s="71">
         <f t="shared" si="4"/>
-        <v>28.809195402298851</v>
+        <v>28.844444444444445</v>
       </c>
       <c r="AR118" s="71">
         <f>IFERROR(VLOOKUP(A118,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21094,7 +21283,7 @@
       </c>
       <c r="AS118" s="71">
         <f t="shared" si="5"/>
-        <v>3.0559158324063915</v>
+        <v>3.0911648745519855</v>
       </c>
     </row>
     <row r="119" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21215,15 +21404,17 @@
       <c r="AM119" s="56">
         <v>24.666666666666671</v>
       </c>
-      <c r="AN119" s="56"/>
+      <c r="AN119" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ119" s="71">
         <f t="shared" si="4"/>
-        <v>23.645977011494253</v>
+        <v>23.646666666666665</v>
       </c>
       <c r="AR119" s="71">
         <f>IFERROR(VLOOKUP(A119,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21231,7 +21422,7 @@
       </c>
       <c r="AS119" s="71">
         <f t="shared" si="5"/>
-        <v>1.9175361512792435</v>
+        <v>1.9182258064516553</v>
       </c>
     </row>
     <row r="120" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21316,11 +21507,13 @@
       <c r="AK120" s="56"/>
       <c r="AL120" s="56"/>
       <c r="AM120" s="56"/>
-      <c r="AN120" s="56"/>
+      <c r="AN120" s="56">
+        <v>27.86666666666666</v>
+      </c>
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ120" s="71" t="str">
         <f t="shared" si="4"/>
@@ -21744,15 +21937,17 @@
         <v>15.8</v>
       </c>
       <c r="AM124" s="56"/>
-      <c r="AN124" s="56"/>
+      <c r="AN124" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ124" s="71">
         <f t="shared" si="4"/>
-        <v>15.997530864197531</v>
+        <v>16.05952380952381</v>
       </c>
       <c r="AR124" s="71">
         <f>IFERROR(VLOOKUP(A124,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21760,7 +21955,7 @@
       </c>
       <c r="AS124" s="71">
         <f t="shared" si="5"/>
-        <v>0.94847190465402065</v>
+        <v>1.0104648499803002</v>
       </c>
     </row>
     <row r="125" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21944,15 +22139,17 @@
       <c r="AM126" s="56">
         <v>10.6</v>
       </c>
-      <c r="AN126" s="56"/>
+      <c r="AN126" s="56">
+        <v>11.8</v>
+      </c>
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>11.81269841269841</v>
+        <v>11.812121212121211</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21960,7 +22157,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>1.1002521966346706</v>
+        <v>1.0996749960574714</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22453,15 +22650,17 @@
       <c r="AM131" s="56">
         <v>18.8</v>
       </c>
-      <c r="AN131" s="56"/>
+      <c r="AN131" s="56">
+        <v>17.55</v>
+      </c>
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.313793103448276</v>
+        <v>18.288333333333334</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22469,7 +22668,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.5208961045443274</v>
+        <v>1.4954363344293853</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22669,15 +22868,17 @@
       <c r="AM133" s="56">
         <v>13.66666666666667</v>
       </c>
-      <c r="AN133" s="56"/>
+      <c r="AN133" s="56">
+        <v>14.46666666666667</v>
+      </c>
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>13.86206896551724</v>
+        <v>13.882222222222222</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22685,7 +22886,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.2267291908634004</v>
+        <v>1.2468824475683817</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22806,15 +23007,17 @@
       <c r="AM134" s="56">
         <v>17.466666666666669</v>
       </c>
-      <c r="AN134" s="56"/>
+      <c r="AN134" s="56">
+        <v>17.2</v>
+      </c>
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>17.772413793103446</v>
+        <v>17.753333333333334</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22822,7 +23025,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.1902349507197769</v>
+        <v>2.1711544909496645</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22943,15 +23146,17 @@
       <c r="AM135" s="56">
         <v>21.45</v>
       </c>
-      <c r="AN135" s="56"/>
+      <c r="AN135" s="56">
+        <v>22.3</v>
+      </c>
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>20.651724137931037</v>
+        <v>20.706666666666667</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22959,7 +23164,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>1.9698435005259078</v>
+        <v>2.0247860292615378</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23076,15 +23281,17 @@
       <c r="AM136" s="56">
         <v>9.6</v>
       </c>
-      <c r="AN136" s="56"/>
+      <c r="AN136" s="56">
+        <v>11.06666666666667</v>
+      </c>
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>11.081481481481479</v>
+        <v>11.080952380952379</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23092,7 +23299,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>0.22383140732501872</v>
+        <v>0.22330230679591878</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23292,15 +23499,17 @@
       <c r="AM138" s="56">
         <v>21.8</v>
       </c>
-      <c r="AN138" s="56"/>
+      <c r="AN138" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>22.158620689655169</v>
+        <v>22.213333333333328</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23308,7 +23517,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.1483995923067702</v>
+        <v>2.2031122359849284</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23429,15 +23638,17 @@
       <c r="AM139" s="56">
         <v>13.6</v>
       </c>
-      <c r="AN139" s="56"/>
+      <c r="AN139" s="56">
+        <v>14.55</v>
+      </c>
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>13.978448275862069</v>
+        <v>13.9975</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23445,7 +23656,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.0742305030280601</v>
+        <v>1.0932822271659912</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23566,15 +23777,17 @@
       <c r="AM140" s="56">
         <v>15.95</v>
       </c>
-      <c r="AN140" s="56"/>
+      <c r="AN140" s="56">
+        <v>17.3</v>
+      </c>
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.327586206896552</v>
+        <v>16.36</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23582,7 +23795,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.73323563512663092</v>
+        <v>0.76564942823007875</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23703,15 +23916,17 @@
       <c r="AM141" s="56">
         <v>12.133333333333329</v>
       </c>
-      <c r="AN141" s="56"/>
+      <c r="AN141" s="56">
+        <v>13.733333333333331</v>
+      </c>
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.386206896551725</v>
+        <v>13.39777777777778</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23719,7 +23934,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.3721774997136755</v>
+        <v>1.3837483809397302</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23838,15 +24053,17 @@
       <c r="AM142" s="56">
         <v>10.75</v>
       </c>
-      <c r="AN142" s="56"/>
+      <c r="AN142" s="56">
+        <v>11.65</v>
+      </c>
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.55</v>
+        <v>11.553448275862069</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23854,7 +24071,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.0210140235181999</v>
+        <v>1.0244622993802679</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23975,15 +24192,17 @@
       <c r="AM143" s="56">
         <v>28.13333333333334</v>
       </c>
-      <c r="AN143" s="56"/>
+      <c r="AN143" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.719540229885059</v>
+        <v>27.744444444444447</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23991,7 +24210,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>1.857600137719178</v>
+        <v>1.8825043522785663</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24105,16 +24324,20 @@
       <c r="AL144" s="56">
         <v>15.46666666666667</v>
       </c>
-      <c r="AM144" s="56"/>
-      <c r="AN144" s="56"/>
+      <c r="AM144" s="56">
+        <v>17</v>
+      </c>
+      <c r="AN144" s="56">
+        <v>15.4</v>
+      </c>
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>15.589743589743591</v>
+        <v>15.633333333333335</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24122,7 +24345,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>-0.12314216417069801</v>
+        <v>-7.9552420580954575E-2</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24243,15 +24466,17 @@
       <c r="AM145" s="56">
         <v>20.466666666666669</v>
       </c>
-      <c r="AN145" s="56"/>
+      <c r="AN145" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>19.540229885057474</v>
+        <v>19.54666666666667</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24259,7 +24484,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>0.49821335055935378</v>
+        <v>0.5046501321685497</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24380,15 +24605,17 @@
       <c r="AM146" s="56">
         <v>31.933333333333341</v>
       </c>
-      <c r="AN146" s="56"/>
+      <c r="AN146" s="56">
+        <v>32.466666666666661</v>
+      </c>
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>29.972413793103446</v>
+        <v>30.055555555555554</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24396,7 +24623,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.2152142553062149</v>
+        <v>1.2983560177583229</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24517,15 +24744,17 @@
       <c r="AM147" s="56">
         <v>25.6</v>
       </c>
-      <c r="AN147" s="56"/>
+      <c r="AN147" s="56">
+        <v>25.333333333333329</v>
+      </c>
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.250574712643683</v>
+        <v>25.253333333333337</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24533,7 +24762,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>1.7465172207803228</v>
+        <v>1.7492758414699772</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24650,15 +24879,17 @@
       <c r="AM148" s="56">
         <v>31.666666666666671</v>
       </c>
-      <c r="AN148" s="56"/>
+      <c r="AN148" s="56">
+        <v>31.06666666666667</v>
+      </c>
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.403703703703698</v>
+        <v>30.42738095238095</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24666,7 +24897,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.762172472848917</v>
+        <v>1.7858497215261693</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24787,15 +25018,17 @@
       <c r="AM149" s="56">
         <v>25.2</v>
       </c>
-      <c r="AN149" s="56"/>
+      <c r="AN149" s="56">
+        <v>25.4</v>
+      </c>
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.565517241379311</v>
+        <v>23.626666666666665</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24803,7 +25036,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>1.68944946842646</v>
+        <v>1.7505988937138142</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24999,15 +25232,17 @@
       <c r="AM151" s="56">
         <v>25.4</v>
       </c>
-      <c r="AN151" s="56"/>
+      <c r="AN151" s="56">
+        <v>23.93333333333333</v>
+      </c>
       <c r="AO151" s="56"/>
       <c r="AP151" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ151" s="71">
         <f t="shared" si="7"/>
-        <v>23.335802469135796</v>
+        <v>23.357142857142851</v>
       </c>
       <c r="AR151" s="71">
         <f>IFERROR(VLOOKUP(A151,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25015,7 +25250,7 @@
       </c>
       <c r="AS151" s="71">
         <f t="shared" si="8"/>
-        <v>1.5232151905151561</v>
+        <v>1.5445555785222105</v>
       </c>
     </row>
     <row r="152" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25431,15 +25666,17 @@
       <c r="AM155" s="56">
         <v>30</v>
       </c>
-      <c r="AN155" s="56"/>
+      <c r="AN155" s="56">
+        <v>28.933333333333341</v>
+      </c>
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>28.898850574712643</v>
+        <v>28.9</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25447,7 +25684,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.1760640138568448</v>
+        <v>1.1772134391442002</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25639,15 +25876,17 @@
       <c r="AM157" s="56">
         <v>30</v>
       </c>
-      <c r="AN157" s="56"/>
+      <c r="AN157" s="56">
+        <v>30</v>
+      </c>
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ157" s="71">
         <f t="shared" si="7"/>
-        <v>29.306666666666676</v>
+        <v>29.333333333333339</v>
       </c>
       <c r="AR157" s="71">
         <f>IFERROR(VLOOKUP(A157,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25655,7 +25894,7 @@
       </c>
       <c r="AS157" s="71">
         <f t="shared" si="8"/>
-        <v>1.722239170057275</v>
+        <v>1.7489058367239387</v>
       </c>
     </row>
     <row r="158" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25770,15 +26009,17 @@
       <c r="AM158" s="56">
         <v>31.8</v>
       </c>
-      <c r="AN158" s="56"/>
+      <c r="AN158" s="56">
+        <v>31.8</v>
+      </c>
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>30.10512820512821</v>
+        <v>30.167901234567903</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25786,7 +26027,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>2.0867160380480101</v>
+        <v>2.1494890674877034</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25901,15 +26142,17 @@
       <c r="AM159" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="AN159" s="56"/>
+      <c r="AN159" s="56">
+        <v>21.733333333333331</v>
+      </c>
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.319230769230771</v>
+        <v>20.371604938271609</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25917,7 +26160,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.3282936545403707</v>
+        <v>1.3806678235812093</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26036,15 +26279,17 @@
       <c r="AM160" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AN160" s="56"/>
+      <c r="AN160" s="56">
+        <v>26.933333333333341</v>
+      </c>
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.042857142857148</v>
+        <v>27.039080459770123</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26286,15 +26531,17 @@
       <c r="AM162" s="56">
         <v>29.866666666666671</v>
       </c>
-      <c r="AN162" s="56"/>
+      <c r="AN162" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.912643678160929</v>
+        <v>28.935555555555563</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26302,7 +26549,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.33910629028665085</v>
+        <v>0.36201816768128481</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26423,15 +26670,17 @@
       <c r="AM163" s="56">
         <v>21.6</v>
       </c>
-      <c r="AN163" s="56"/>
+      <c r="AN163" s="56">
+        <v>22.133333333333329</v>
+      </c>
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.422988505747124</v>
+        <v>21.446666666666665</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26439,7 +26688,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.17356469014654508</v>
+        <v>0.19724285106608619</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26560,15 +26809,17 @@
       <c r="AM164" s="56">
         <v>25.85</v>
       </c>
-      <c r="AN164" s="56"/>
+      <c r="AN164" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.398275862068967</v>
+        <v>25.416666666666671</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26576,7 +26827,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.600348252908887</v>
+        <v>1.6187390575065912</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26905,15 +27156,17 @@
       <c r="AM167" s="56">
         <v>21.4</v>
       </c>
-      <c r="AN167" s="56"/>
+      <c r="AN167" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.68888888888889</v>
+        <v>20.711904761904766</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26921,7 +27174,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.6533210792782498</v>
+        <v>1.6763369522941254</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27038,15 +27291,17 @@
       <c r="AM168" s="56">
         <v>28.1</v>
       </c>
-      <c r="AN168" s="56"/>
+      <c r="AN168" s="56">
+        <v>27.95</v>
+      </c>
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.837037037037046</v>
+        <v>27.841071428571439</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27054,7 +27309,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.7711725709704673</v>
+        <v>1.7752069625048605</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27175,15 +27430,17 @@
       <c r="AM169" s="56">
         <v>9</v>
       </c>
-      <c r="AN169" s="56"/>
+      <c r="AN169" s="56">
+        <v>9</v>
+      </c>
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>9.0189655172413783</v>
+        <v>9.0183333333333326</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27191,7 +27448,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.47684123588684102</v>
+        <v>0.47620905197879537</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27296,15 +27553,17 @@
       <c r="AM170" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="AN170" s="56"/>
+      <c r="AN170" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ170" s="71">
         <f t="shared" si="7"/>
-        <v>25.098412698412695</v>
+        <v>25.212121212121211</v>
       </c>
       <c r="AR170" s="71">
         <f>IFERROR(VLOOKUP(A170,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27312,7 +27571,7 @@
       </c>
       <c r="AS170" s="71">
         <f t="shared" si="8"/>
-        <v>1.007788756550223</v>
+        <v>1.1214972702587396</v>
       </c>
     </row>
     <row r="171" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27431,15 +27690,17 @@
       <c r="AM171" s="56">
         <v>21.4</v>
       </c>
-      <c r="AN171" s="56"/>
+      <c r="AN171" s="56">
+        <v>22.86666666666666</v>
+      </c>
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>20.764285714285712</v>
+        <v>20.836781609195402</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27447,7 +27708,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>1.8353596920337942</v>
+        <v>1.9078555869434837</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27564,15 +27825,17 @@
       <c r="AM172" s="56">
         <v>26.3</v>
       </c>
-      <c r="AN172" s="56"/>
+      <c r="AN172" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.755555555555556</v>
+        <v>25.762499999999999</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27580,7 +27843,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.3169271870436781</v>
+        <v>1.3238716314881209</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27701,15 +27964,17 @@
       <c r="AM173" s="56">
         <v>26.2</v>
       </c>
-      <c r="AN173" s="56"/>
+      <c r="AN173" s="56">
+        <v>26.25</v>
+      </c>
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.150287356321847</v>
+        <v>25.186944444444453</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27717,7 +27982,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.0958787541713164</v>
+        <v>1.1325358422939225</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28242,15 +28507,17 @@
       <c r="AM178" s="56">
         <v>25.866666666666671</v>
       </c>
-      <c r="AN178" s="56"/>
+      <c r="AN178" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>25.230555555555554</v>
+        <v>25.295999999999999</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28258,7 +28525,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.6782752086766628</v>
+        <v>0.74371965312110788</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28371,15 +28638,17 @@
       <c r="AM179" s="56">
         <v>19.95</v>
       </c>
-      <c r="AN179" s="56"/>
+      <c r="AN179" s="56">
+        <v>20.100000000000001</v>
+      </c>
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.61</v>
+        <v>18.667307692307691</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28387,7 +28656,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>1.0224163164833477</v>
+        <v>1.0797240087910396</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28587,15 +28856,17 @@
       <c r="AM181" s="56">
         <v>29.4</v>
       </c>
-      <c r="AN181" s="56"/>
+      <c r="AN181" s="56">
+        <v>32.533333333333331</v>
+      </c>
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ181" s="71">
         <f t="shared" si="7"/>
-        <v>30.956321839080456</v>
+        <v>31.008888888888883</v>
       </c>
       <c r="AR181" s="71">
         <f>IFERROR(VLOOKUP(A181,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28603,7 +28874,7 @@
       </c>
       <c r="AS181" s="71">
         <f t="shared" si="8"/>
-        <v>2.4230854515106444</v>
+        <v>2.4756525013190718</v>
       </c>
     </row>
     <row r="182" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28882,15 +29153,17 @@
       <c r="AM184" s="56">
         <v>28.066666666666659</v>
       </c>
-      <c r="AN184" s="56"/>
+      <c r="AN184" s="56">
+        <v>29.666666666666671</v>
+      </c>
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>28.141379310344828</v>
+        <v>28.19222222222222</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28898,7 +29171,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.5030080927278391</v>
+        <v>1.5538510046052316</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29011,15 +29284,17 @@
       <c r="AM185" s="56">
         <v>28.733333333333331</v>
       </c>
-      <c r="AN185" s="56"/>
+      <c r="AN185" s="56">
+        <v>29.733333333333331</v>
+      </c>
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ185" s="71">
         <f t="shared" si="7"/>
-        <v>28.930666666666667</v>
+        <v>28.96153846153846</v>
       </c>
       <c r="AR185" s="71">
         <f>IFERROR(VLOOKUP(A185,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29027,7 +29302,7 @@
       </c>
       <c r="AS185" s="71">
         <f t="shared" si="8"/>
-        <v>1.3220343816552962</v>
+        <v>1.3529061765270889</v>
       </c>
     </row>
     <row r="186" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29306,15 +29581,17 @@
       <c r="AM188" s="56">
         <v>17.600000000000001</v>
       </c>
-      <c r="AN188" s="56"/>
+      <c r="AN188" s="56">
+        <v>18.93333333333333</v>
+      </c>
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>17.298850574712649</v>
+        <v>17.353333333333339</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29322,7 +29599,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.3032585851809184</v>
+        <v>1.3577413438016084</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29566,15 +29843,17 @@
       <c r="AM190" s="56">
         <v>29.466666666666669</v>
       </c>
-      <c r="AN190" s="56"/>
+      <c r="AN190" s="56">
+        <v>31.4</v>
+      </c>
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>30.494252873563219</v>
+        <v>30.524444444444445</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29582,7 +29861,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>1.5777292120807509</v>
+        <v>1.6079207829619762</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29703,15 +29982,17 @@
       <c r="AM191" s="56">
         <v>18.649999999999999</v>
       </c>
-      <c r="AN191" s="56"/>
+      <c r="AN191" s="56">
+        <v>20.2</v>
+      </c>
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>18.558620689655172</v>
+        <v>18.613333333333333</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29719,7 +30000,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>1.1714016749945628</v>
+        <v>1.2261143186727246</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29840,15 +30121,17 @@
       <c r="AM192" s="56">
         <v>26.4</v>
       </c>
-      <c r="AN192" s="56"/>
+      <c r="AN192" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.236781609195415</v>
+        <v>26.255555555555567</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29856,7 +30139,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.99227442837724311</v>
+        <v>1.0110483747373955</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -29971,15 +30254,17 @@
       <c r="AM193" s="56">
         <v>29.55</v>
       </c>
-      <c r="AN193" s="56"/>
+      <c r="AN193" s="56">
+        <v>29.25</v>
+      </c>
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ193" s="71">
         <f t="shared" si="7"/>
-        <v>27.27884615384615</v>
+        <v>27.351851851851848</v>
       </c>
       <c r="AR193" s="71">
         <f>IFERROR(VLOOKUP(A193,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -29987,7 +30272,7 @@
       </c>
       <c r="AS193" s="71">
         <f t="shared" si="8"/>
-        <v>0.92607661383697959</v>
+        <v>0.99908231184267748</v>
       </c>
     </row>
     <row r="194" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30108,15 +30393,17 @@
       <c r="AM194" s="56">
         <v>21.8</v>
       </c>
-      <c r="AN194" s="56"/>
+      <c r="AN194" s="56">
+        <v>23</v>
+      </c>
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.243678160919536</v>
+        <v>21.30222222222222</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30124,7 +30411,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-0.36398363613889373</v>
+        <v>-0.30543957483621043</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30245,15 +30532,17 @@
       <c r="AM195" s="56">
         <v>27.133333333333329</v>
       </c>
-      <c r="AN195" s="56"/>
+      <c r="AN195" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ195" s="71">
         <f t="shared" si="7"/>
-        <v>27.533333333333335</v>
+        <v>27.602222222222224</v>
       </c>
       <c r="AR195" s="71">
         <f>IFERROR(VLOOKUP(A195,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30261,7 +30550,7 @@
       </c>
       <c r="AS195" s="71">
         <f t="shared" si="8"/>
-        <v>1.845845123623576</v>
+        <v>1.914734012512465</v>
       </c>
     </row>
     <row r="196" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30382,15 +30671,17 @@
       <c r="AM196" s="56">
         <v>21.8</v>
       </c>
-      <c r="AN196" s="56"/>
+      <c r="AN196" s="56">
+        <v>23.93333333333333</v>
+      </c>
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>22.04137931034483</v>
+        <v>22.104444444444443</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30398,7 +30689,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>1.8176228388195597</v>
+        <v>1.8806879729191728</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30519,15 +30810,17 @@
       <c r="AM197" s="56">
         <v>26.93333333333333</v>
       </c>
-      <c r="AN197" s="56"/>
+      <c r="AN197" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.970114942528735</v>
+        <v>26.024444444444445</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30535,7 +30828,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.8427319413582062</v>
+        <v>1.8970614432739161</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30656,15 +30949,17 @@
       <c r="AM198" s="56">
         <v>21.55</v>
       </c>
-      <c r="AN198" s="56"/>
+      <c r="AN198" s="56">
+        <v>22.7</v>
+      </c>
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.601724137931029</v>
+        <v>21.638333333333328</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30793,15 +31088,17 @@
       <c r="AM199" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="AN199" s="56"/>
+      <c r="AN199" s="56">
+        <v>16.93333333333333</v>
+      </c>
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.570114942528736</v>
+        <v>16.582222222222221</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30809,7 +31106,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.78245453633754636</v>
+        <v>0.79456181603103104</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -30930,15 +31227,17 @@
       <c r="AM200" s="56">
         <v>14.65</v>
       </c>
-      <c r="AN200" s="56"/>
+      <c r="AN200" s="56">
+        <v>14.3</v>
+      </c>
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.625862068965516</v>
+        <v>14.615</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -30946,7 +31245,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.2602496011818758</v>
+        <v>1.2493875322163603</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31549,15 +31848,17 @@
       <c r="AM205" s="56">
         <v>14.85</v>
       </c>
-      <c r="AN205" s="56"/>
+      <c r="AN205" s="56">
+        <v>15</v>
+      </c>
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>14.548275862068966</v>
+        <v>14.563333333333334</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31565,7 +31866,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.1333817452512953</v>
+        <v>1.1484392165156638</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31668,17 +31969,21 @@
       <c r="AI206" s="56"/>
       <c r="AJ206" s="56"/>
       <c r="AK206" s="56"/>
-      <c r="AL206" s="56"/>
-      <c r="AM206" s="56"/>
+      <c r="AL206" s="56">
+        <v>13.2</v>
+      </c>
+      <c r="AM206" s="56">
+        <v>13.4</v>
+      </c>
       <c r="AN206" s="56"/>
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v>13.552380952380954</v>
+        <v>13.530434782608696</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31789,15 +32094,17 @@
       <c r="AM207" s="56">
         <v>14.266666666666669</v>
       </c>
-      <c r="AN207" s="56"/>
+      <c r="AN207" s="56">
+        <v>14.46666666666667</v>
+      </c>
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ207" s="71">
         <f t="shared" si="10"/>
-        <v>14.229999999999995</v>
+        <v>14.241269841269839</v>
       </c>
       <c r="AR207" s="71">
         <f>IFERROR(VLOOKUP(A207,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -31805,7 +32112,7 @@
       </c>
       <c r="AS207" s="71">
         <f t="shared" si="11"/>
-        <v>0.66922419493727503</v>
+        <v>0.68049403620711857</v>
       </c>
     </row>
     <row r="208" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -31924,15 +32231,17 @@
       <c r="AM208" s="56">
         <v>14.4</v>
       </c>
-      <c r="AN208" s="56"/>
+      <c r="AN208" s="56">
+        <v>14.95</v>
+      </c>
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.182142857142853</v>
+        <v>14.208620689655168</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -32061,15 +32370,17 @@
       <c r="AM209" s="56">
         <v>10.75</v>
       </c>
-      <c r="AN209" s="56"/>
+      <c r="AN209" s="56">
+        <v>11.05</v>
+      </c>
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.077586206896553</v>
+        <v>11.07666666666667</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -32322,16 +32633,20 @@
       <c r="AL211" s="56">
         <v>9.0500000000000007</v>
       </c>
-      <c r="AM211" s="56"/>
-      <c r="AN211" s="56"/>
+      <c r="AM211" s="56">
+        <v>8.5499999999999989</v>
+      </c>
+      <c r="AN211" s="56">
+        <v>8.6</v>
+      </c>
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.638461538461538</v>
+        <v>8.6339285714285712</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -32339,7 +32654,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.5583286567711383</v>
+        <v>0.5537956897381715</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -32460,15 +32775,17 @@
       <c r="AM212" s="56">
         <v>27.55</v>
       </c>
-      <c r="AN212" s="56"/>
+      <c r="AN212" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>25.815517241379297</v>
+        <v>25.824999999999989</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
